--- a/output/stock_quant_scores/TSLA_balance_df.xlsx
+++ b/output/stock_quant_scores/TSLA_balance_df.xlsx
@@ -1804,25 +1804,35 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>8873000000</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>7395000000</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>30189000000</v>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>329000000</v>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>30548000000</v>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
@@ -1840,7 +1850,9 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>19705000000</v>
+      </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
@@ -1858,7 +1870,9 @@
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>62131000000</v>
+      </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
@@ -1875,12 +1889,16 @@
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+      <c r="BP6" t="n">
+        <v>27100000000</v>
+      </c>
       <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="n">
         <v>1346000000</v>
       </c>
-      <c r="BS6" t="inlineStr"/>
+      <c r="BS6" t="n">
+        <v>5757000000</v>
+      </c>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
@@ -1889,7 +1907,9 @@
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="inlineStr"/>
+      <c r="CB6" t="n">
+        <v>17576000000</v>
+      </c>
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
     </row>
